--- a/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1f7842c9540f452e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2bbcf8e34c604f3a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2bbcf8e34c604f3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfe2d32839e5341f8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfe2d32839e5341f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R53b2ae6d151c4021"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R53b2ae6d151c4021"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rac1c8814c9634bc6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rac1c8814c9634bc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5bb3ee149b41448f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5bb3ee149b41448f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rff98f784d3c7458e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rff98f784d3c7458e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R333b0f32648741ea"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R333b0f32648741ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7ad10a010ee045d6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7ad10a010ee045d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R07b0f79f2cdb4f5e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R07b0f79f2cdb4f5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R46b78eff0c854301"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R46b78eff0c854301"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc79edce69f6e48bf"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc79edce69f6e48bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R308adcddfa53427f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R308adcddfa53427f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raae6e4a650884918"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raae6e4a650884918"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd407f0ad59f34e58"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd407f0ad59f34e58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rac61341c07144bb7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rac61341c07144bb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R42e00f4094c740a1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R42e00f4094c740a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R13e2d0b0bbb74511"/>
   </x:sheets>
 </x:workbook>
 </file>
